--- a/data/trans_orig/Q17F_D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario</t>
+          <t>Tiempo de espera medio en días hasta la consulta en el centro sanitario (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 23,81</t>
+          <t>6,86; 26,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 15,43</t>
+          <t>5,6; 16,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 21,15</t>
+          <t>3,63; 19,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 14,5</t>
+          <t>3,67; 12,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 15,06</t>
+          <t>4,7; 16,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 13,21</t>
+          <t>3,06; 13,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 26,15</t>
+          <t>8,77; 27,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 39,96</t>
+          <t>13,4; 39,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 16,88</t>
+          <t>6,72; 16,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,77</t>
+          <t>4,51; 11,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,88; 19,51</t>
+          <t>7,96; 20,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 25,17</t>
+          <t>10,03; 26,16</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 50,03</t>
+          <t>9,17; 43,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 17,65</t>
+          <t>5,81; 18,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 14,97</t>
+          <t>5,21; 14,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,23; 71,45</t>
+          <t>13,59; 71,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,71; 24,62</t>
+          <t>10,42; 25,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 21,24</t>
+          <t>6,63; 20,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 21,24</t>
+          <t>8,83; 21,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,92; 47,82</t>
+          <t>17,76; 46,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 25,88</t>
+          <t>11,6; 28,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 17,52</t>
+          <t>7,28; 16,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 17,33</t>
+          <t>8,33; 16,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,2; 48,74</t>
+          <t>17,83; 44,35</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 37,17</t>
+          <t>3,34; 32,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 20,52</t>
+          <t>4,6; 18,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 18,33</t>
+          <t>3,15; 17,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 31,67</t>
+          <t>8,54; 32,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,3</t>
+          <t>2,3; 6,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 20,72</t>
+          <t>4,52; 21,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 24,7</t>
+          <t>5,55; 24,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,59</t>
+          <t>8,08; 15,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 15,95</t>
+          <t>3,56; 15,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 16,1</t>
+          <t>5,64; 17,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 18,4</t>
+          <t>5,69; 17,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,44; 20,71</t>
+          <t>9,32; 20,73</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 31,59</t>
+          <t>8,72; 30,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 24,29</t>
+          <t>6,98; 23,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 25,1</t>
+          <t>7,79; 26,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,36; 101,17</t>
+          <t>26,4; 108,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,25</t>
+          <t>2,11; 7,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 18,64</t>
+          <t>5,86; 18,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 24,56</t>
+          <t>8,5; 22,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 23,6</t>
+          <t>6,45; 24,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 12,94</t>
+          <t>4,85; 13,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 17,03</t>
+          <t>7,48; 16,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 21,6</t>
+          <t>9,59; 20,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,75; 40,98</t>
+          <t>11,45; 40,07</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 17,7</t>
+          <t>3,32; 17,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 13,33</t>
+          <t>1,92; 11,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 18,8</t>
+          <t>2,77; 19,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 133,91</t>
+          <t>20,83; 140,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 15,23</t>
+          <t>5,28; 15,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 11,55</t>
+          <t>4,62; 11,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 33,68</t>
+          <t>4,15; 35,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 16,03</t>
+          <t>7,75; 15,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 13,4</t>
+          <t>5,43; 13,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,16</t>
+          <t>4,24; 8,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 24,72</t>
+          <t>5,38; 25,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,6; 74,57</t>
+          <t>14,09; 69,1</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,01</t>
+          <t>1,65; 13,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 16,26</t>
+          <t>5,07; 17,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,75</t>
+          <t>2,47; 7,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 22,77</t>
+          <t>6,46; 24,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,0; 29,17</t>
+          <t>4,38; 30,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,87; 20,29</t>
+          <t>6,32; 20,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,44</t>
+          <t>3,65; 10,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,06; 30,86</t>
+          <t>7,59; 31,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 19,65</t>
+          <t>4,06; 20,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 15,98</t>
+          <t>6,66; 15,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,06</t>
+          <t>3,39; 7,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,42; 22,04</t>
+          <t>8,66; 23,34</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,01</t>
+          <t>6,8; 14,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 19,17</t>
+          <t>8,7; 19,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,29; 28,61</t>
+          <t>12,68; 30,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,42; 49,49</t>
+          <t>22,34; 50,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,48; 18,37</t>
+          <t>7,58; 18,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,95; 20,57</t>
+          <t>9,25; 20,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 22,89</t>
+          <t>9,48; 22,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,25; 36,34</t>
+          <t>20,24; 36,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,13; 15,52</t>
+          <t>7,96; 15,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,88; 17,27</t>
+          <t>9,94; 17,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,2; 22,77</t>
+          <t>12,27; 22,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,43; 38,49</t>
+          <t>22,35; 37,74</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,29</t>
+          <t>4,12; 11,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,96</t>
+          <t>5,75; 14,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,84; 11,42</t>
+          <t>4,85; 11,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 19,94</t>
+          <t>10,71; 20,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,25; 14,46</t>
+          <t>5,42; 15,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 15,46</t>
+          <t>5,76; 15,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,07; 34,56</t>
+          <t>11,23; 36,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,11; 34,73</t>
+          <t>18,23; 35,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,49</t>
+          <t>5,35; 11,49</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,09</t>
+          <t>6,63; 13,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 22,85</t>
+          <t>9,25; 22,6</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,42; 26,16</t>
+          <t>16,12; 26,58</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,2; 14,57</t>
+          <t>8,3; 14,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,19</t>
+          <t>8,15; 12,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,81</t>
+          <t>7,95; 12,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,03; 31,65</t>
+          <t>19,08; 30,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,44</t>
+          <t>7,36; 11,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,18</t>
+          <t>8,03; 12,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,15; 18,26</t>
+          <t>11,11; 17,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,83; 24,8</t>
+          <t>16,08; 24,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,49</t>
+          <t>8,25; 11,52</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,66; 11,82</t>
+          <t>8,55; 11,49</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,45; 14,83</t>
+          <t>10,3; 14,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,76; 26,01</t>
+          <t>18,85; 25,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q17F_D_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,71</t>
+          <t>20,94</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 26,49</t>
+          <t>6,79; 27,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 16,76</t>
+          <t>5,22; 16,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 19,38</t>
+          <t>3,75; 21,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 12,97</t>
+          <t>4,31; 15,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 16,49</t>
+          <t>4,75; 16,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 13,5</t>
+          <t>3,01; 13,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 27,05</t>
+          <t>8,55; 28,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 39,95</t>
+          <t>12,8; 40,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 16,45</t>
+          <t>6,97; 17,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,34</t>
+          <t>4,57; 11,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 20,19</t>
+          <t>7,79; 19,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,03; 26,16</t>
+          <t>10,31; 25,9</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,94</t>
+          <t>25,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,89</t>
+          <t>27,05</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 43,92</t>
+          <t>9,57; 47,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 18,07</t>
+          <t>5,72; 18,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 14,86</t>
+          <t>5,26; 14,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,59; 71,51</t>
+          <t>12,59; 72,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 25,53</t>
+          <t>10,45; 25,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 20,8</t>
+          <t>5,99; 21,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 21,79</t>
+          <t>8,95; 21,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,76; 46,42</t>
+          <t>18,98; 45,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 28,62</t>
+          <t>11,63; 27,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 16,66</t>
+          <t>6,98; 17,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 16,83</t>
+          <t>8,61; 17,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 44,35</t>
+          <t>18,76; 49,48</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,05</t>
+          <t>15,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,78</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 32,33</t>
+          <t>3,2; 32,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 18,56</t>
+          <t>4,48; 19,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 17,85</t>
+          <t>3,04; 17,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 32,11</t>
+          <t>8,46; 29,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,42</t>
+          <t>2,2; 6,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 21,38</t>
+          <t>4,17; 21,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 24,53</t>
+          <t>5,59; 27,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 15,48</t>
+          <t>7,72; 15,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 15,38</t>
+          <t>3,58; 15,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 17,83</t>
+          <t>5,23; 16,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 17,99</t>
+          <t>5,54; 17,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,32; 20,73</t>
+          <t>9,21; 19,68</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,81</t>
+          <t>47,87</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>21,83</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7,57</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11,23</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>13,67</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,57</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11,23</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13,67</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,22</t>
+          <t>32,82</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 30,2</t>
+          <t>9,17; 32,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 23,25</t>
+          <t>6,25; 21,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 26,61</t>
+          <t>8,17; 24,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,4; 108,26</t>
+          <t>28,19; 95,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,96</t>
+          <t>2,16; 7,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 18,1</t>
+          <t>5,68; 18,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 22,89</t>
+          <t>8,58; 23,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 24,13</t>
+          <t>15,66; 33,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 13,47</t>
+          <t>4,6; 12,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 16,94</t>
+          <t>7,38; 16,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 20,48</t>
+          <t>9,42; 21,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 40,07</t>
+          <t>22,67; 54,0</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57,01</t>
+          <t>56,57</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,76</t>
+          <t>10,63</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>29,22</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 17,2</t>
+          <t>3,37; 16,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,38</t>
+          <t>1,91; 12,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 19,78</t>
+          <t>2,43; 19,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20,83; 140,82</t>
+          <t>20,58; 152,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 15,74</t>
+          <t>5,43; 14,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 11,31</t>
+          <t>4,65; 11,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 35,14</t>
+          <t>4,22; 40,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,75; 15,74</t>
+          <t>7,86; 16,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,09</t>
+          <t>5,36; 13,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,95</t>
+          <t>4,16; 9,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 25,55</t>
+          <t>5,16; 26,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 69,1</t>
+          <t>14,42; 66,28</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>11,17</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,73</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>12,91</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 13,01</t>
+          <t>1,66; 12,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 17,57</t>
+          <t>4,87; 16,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,68</t>
+          <t>2,37; 8,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 24,49</t>
+          <t>6,48; 21,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 30,01</t>
+          <t>3,77; 28,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,32; 20,53</t>
+          <t>5,7; 19,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,67</t>
+          <t>3,49; 11,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,59; 31,06</t>
+          <t>7,94; 33,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,06; 20,54</t>
+          <t>4,18; 19,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,66; 15,8</t>
+          <t>6,64; 15,85</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,76</t>
+          <t>3,35; 7,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,66; 23,34</t>
+          <t>8,51; 22,07</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32,82</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,87</t>
+          <t>27,34</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,33</t>
+          <t>29,03</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,83</t>
+          <t>6,75; 13,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,7; 19,33</t>
+          <t>8,72; 19,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,68; 30,5</t>
+          <t>12,9; 29,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,34; 50,15</t>
+          <t>22,35; 48,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,58; 18,34</t>
+          <t>7,64; 18,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 20,14</t>
+          <t>8,95; 18,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 22,37</t>
+          <t>9,75; 23,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,24; 36,06</t>
+          <t>21,86; 36,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 15,33</t>
+          <t>8,01; 15,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,94; 17,53</t>
+          <t>9,52; 17,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,27; 22,3</t>
+          <t>12,37; 22,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,35; 37,74</t>
+          <t>23,1; 36,28</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>15,58</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23,95</t>
+          <t>23,97</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,85</t>
+          <t>20,48</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,12; 11,68</t>
+          <t>4,14; 11,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,75; 14,38</t>
+          <t>5,46; 13,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,61</t>
+          <t>5,05; 11,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,26</t>
+          <t>11,3; 23,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,72</t>
+          <t>5,5; 14,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,76; 15,22</t>
+          <t>5,9; 16,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,23; 36,49</t>
+          <t>11,05; 34,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,23; 35,06</t>
+          <t>18,31; 34,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,49</t>
+          <t>5,36; 11,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,42</t>
+          <t>6,37; 12,91</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,25; 22,6</t>
+          <t>8,97; 23,67</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,12; 26,58</t>
+          <t>16,2; 26,83</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23,77</t>
+          <t>24,21</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>20,76</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,01</t>
+          <t>23,29</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,3; 14,3</t>
+          <t>8,24; 15,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,21</t>
+          <t>8,18; 12,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,46</t>
+          <t>7,91; 12,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,08; 30,77</t>
+          <t>19,91; 31,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,28</t>
+          <t>7,57; 11,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,03; 12,11</t>
+          <t>8,17; 12,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,63</t>
+          <t>10,97; 17,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,08; 24,38</t>
+          <t>19,79; 26,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,52</t>
+          <t>8,13; 11,58</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,55; 11,49</t>
+          <t>8,67; 11,61</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,3; 14,7</t>
+          <t>10,25; 14,47</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,85; 25,82</t>
+          <t>20,54; 26,97</t>
         </is>
       </c>
     </row>
